--- a/data/trans_orig/P64D$andando_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según cómo se desplaza desde su casa al centro de trabajo/estudios, mediante, al menos, una de las opciones (multirrespuesta) en 2023</t>
+          <t>Población según cómo se desplaza desde su casa al centro de trabajo/estudios, mediante, al menos, una de las opciones (multirrespuesta) en 2023 (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42629</t>
+          <t>42473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37752</t>
+          <t>38177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>37357</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73807</t>
+          <t>71548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36301</t>
+          <t>34818</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65919</t>
+          <t>64537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33815</t>
+          <t>35185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56217</t>
+          <t>57556</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76254</t>
+          <t>76452</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114986</t>
+          <t>115747</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,35%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>25881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27766</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18494</t>
+          <t>18555</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44380</t>
+          <t>44993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -1182,82 +1182,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3610</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>164</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>881</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24491</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26715</t>
+          <t>27205</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55020</t>
+          <t>55509</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91793</t>
+          <t>92152</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51191</t>
+          <t>50695</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130388</t>
+          <t>131095</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120399</t>
+          <t>118887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201269</t>
+          <t>200015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>205182</t>
+          <t>215953</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275999</t>
+          <t>251899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>237237</t>
+          <t>236192</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>278227</t>
+          <t>277518</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95384</t>
+          <t>86739</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>231798</t>
+          <t>232235</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>296295</t>
+          <t>307445</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>496693</t>
+          <t>497678</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13686</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>36062</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>12116</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37844</t>
+          <t>37413</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32105</t>
+          <t>32978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66948</t>
+          <t>66552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>13844</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35669</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>48846</t>
+          <t>49350</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80032</t>
+          <t>78743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115113</t>
+          <t>112482</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105786</t>
+          <t>106854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>134763</t>
+          <t>135065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192955</t>
+          <t>192941</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>239231</t>
+          <t>238101</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>339768</t>
+          <t>339562</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>375304</t>
+          <t>376239</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>214085</t>
+          <t>214086</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>244375</t>
+          <t>244663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>561435</t>
+          <t>562862</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>610531</t>
+          <t>609438</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24917</t>
+          <t>25267</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48994</t>
+          <t>49773</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21160</t>
+          <t>21800</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39169</t>
+          <t>39680</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51923</t>
+          <t>51387</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80768</t>
+          <t>79660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>12886</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>14271</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28984</t>
+          <t>28812</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20125</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40805</t>
+          <t>40824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38989</t>
+          <t>37905</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>161779</t>
+          <t>159310</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115534</t>
+          <t>115440</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>167784</t>
+          <t>167996</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134831</t>
+          <t>119995</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>323747</t>
+          <t>324980</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>18377</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>583863</t>
+          <t>585088</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>706915</t>
+          <t>703949</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>281030</t>
+          <t>280896</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>334552</t>
+          <t>333127</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>869965</t>
+          <t>872736</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1060220</t>
+          <t>1072008</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49189</t>
+          <t>46365</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38019</t>
+          <t>37569</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68962</t>
+          <t>71633</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>37617</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>108757</t>
+          <t>108163</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8015</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26482</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23070</t>
+          <t>23529</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>43654</t>
+          <t>43321</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>65020</t>
+          <t>66792</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>93512</t>
+          <t>95620</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>85732</t>
+          <t>83650</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>106131</t>
+          <t>105197</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>157460</t>
+          <t>156354</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>193502</t>
+          <t>192625</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>913</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>198940</t>
+          <t>198731</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>227423</t>
+          <t>227136</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103109</t>
+          <t>102070</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>124183</t>
+          <t>124629</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>309950</t>
+          <t>308563</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>346123</t>
+          <t>347459</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39146</t>
+          <t>38322</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16973</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30520</t>
+          <t>31475</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>40020</t>
+          <t>40282</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>62459</t>
+          <t>63216</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18790</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>17484</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>15955</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>31494</t>
+          <t>31697</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12727</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13633</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23702</t>
+          <t>23930</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,62 +4288,62 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>3489</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>919</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>532</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,62 +4627,62 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>3584</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>421</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -4935,97 +4935,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="W41" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5161,97 +5161,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5274,97 +5274,97 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="W44" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5387,97 +5387,97 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="W45" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>256105</t>
+          <t>255714</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>453789</t>
+          <t>451392</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>418556</t>
+          <t>423386</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>546259</t>
+          <t>541374</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>676360</t>
+          <t>691675</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>977176</t>
+          <t>977130</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>301237</t>
+          <t>299486</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>31321</t>
+          <t>31386</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>398185</t>
+          <t>377216</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1457763</t>
+          <t>1453831</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1673040</t>
+          <t>1670403</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>738808</t>
+          <t>735063</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>939288</t>
+          <t>936876</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2249815</t>
+          <t>2257817</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2625071</t>
+          <t>2597394</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>83786</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>158391</t>
+          <t>158237</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>122483</t>
+          <t>119889</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>177543</t>
+          <t>174491</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>213515</t>
+          <t>217072</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>319655</t>
+          <t>317880</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>27537</t>
+          <t>27774</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>15689</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>37855</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>48465</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>97633</t>
+          <t>99132</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>38912</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>66157</t>
+          <t>66794</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>96243</t>
+          <t>95297</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>151993</t>
+          <t>152098</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">

--- a/data/trans_orig/P64D$andando_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27341</t>
+          <t>36675</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>22170</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42473</t>
+          <t>52700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>30602</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>20065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>53483</t>
+          <t>67277</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37357</t>
+          <t>48510</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71548</t>
+          <t>88059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51029</t>
+          <t>52600</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34818</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64537</t>
+          <t>66726</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46419</t>
+          <t>49614</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35185</t>
+          <t>36623</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57556</t>
+          <t>62096</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>97447</t>
+          <t>102214</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76452</t>
+          <t>82160</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115747</t>
+          <t>123104</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28186</t>
+          <t>30601</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30388</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18555</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44993</t>
+          <t>53218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70604</t>
+          <t>81078</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55509</t>
+          <t>62150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92152</t>
+          <t>104101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>99018</t>
+          <t>114031</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50695</t>
+          <t>97448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131095</t>
+          <t>131006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>169622</t>
+          <t>195109</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118887</t>
+          <t>166351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200015</t>
+          <t>219780</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70957</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>215953</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>74322</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251899</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>258590</t>
+          <t>284006</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>236192</t>
+          <t>261756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>277518</t>
+          <t>305995</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181059</t>
+          <t>192900</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86739</t>
+          <t>174582</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>232235</t>
+          <t>210496</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>439649</t>
+          <t>476907</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>307445</t>
+          <t>448344</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>497678</t>
+          <t>509677</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>20419</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36062</t>
+          <t>49304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>22912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37413</t>
+          <t>46613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48669</t>
+          <t>66155</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32978</t>
+          <t>50594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66552</t>
+          <t>86153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13823</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19909</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>24822</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38970</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19141</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>31976</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>49350</t>
+          <t>54927</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>94952</t>
+          <t>113677</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78743</t>
+          <t>94611</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112482</t>
+          <t>134922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>119812</t>
+          <t>138826</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>106854</t>
+          <t>122907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135065</t>
+          <t>154826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>214764</t>
+          <t>252503</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192941</t>
+          <t>228056</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>238101</t>
+          <t>279422</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>357882</t>
+          <t>408355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>339562</t>
+          <t>385208</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>376239</t>
+          <t>427829</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>229529</t>
+          <t>253953</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>214086</t>
+          <t>238284</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>244663</t>
+          <t>270360</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>587411</t>
+          <t>662308</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>562862</t>
+          <t>636813</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>609438</t>
+          <t>688494</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36063</t>
+          <t>43602</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49773</t>
+          <t>57580</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29149</t>
+          <t>34531</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>45814</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>78133</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51387</t>
+          <t>63538</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79660</t>
+          <t>96356</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -2541,17 +2541,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12886</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>23348</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28812</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>29621</t>
+          <t>37433</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20561</t>
+          <t>27304</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40824</t>
+          <t>51597</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>102125</t>
+          <t>112614</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37905</t>
+          <t>95405</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159310</t>
+          <t>133915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>146907</t>
+          <t>155096</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115440</t>
+          <t>139350</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>167996</t>
+          <t>171343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>249031</t>
+          <t>267710</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119995</t>
+          <t>242945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>324980</t>
+          <t>293983</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>22334</t>
+          <t>27820</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>643064</t>
+          <t>426416</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>585088</t>
+          <t>404635</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>703949</t>
+          <t>444088</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>302625</t>
+          <t>292663</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>280896</t>
+          <t>275989</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>333127</t>
+          <t>307534</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>945689</t>
+          <t>719079</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>872736</t>
+          <t>691534</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1072008</t>
+          <t>743507</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>74,46%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>33650</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>23505</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46365</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>51369</t>
+          <t>54986</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37569</t>
+          <t>43338</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71633</t>
+          <t>66997</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>79484</t>
+          <t>88636</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37617</t>
+          <t>73099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>108163</t>
+          <t>105932</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>11264</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,22 +3258,22 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26482</t>
+          <t>25667</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15835</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23529</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>34753</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>25469</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>43321</t>
+          <t>46549</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>79386</t>
+          <t>84611</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66792</t>
+          <t>69580</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>95620</t>
+          <t>100522</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>95243</t>
+          <t>105135</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>83650</t>
+          <t>93610</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>105197</t>
+          <t>116943</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>174629</t>
+          <t>189746</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>170084</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>192625</t>
+          <t>210753</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>212979</t>
+          <t>227382</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>198731</t>
+          <t>209890</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>227136</t>
+          <t>243719</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>113956</t>
+          <t>123667</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>102070</t>
+          <t>110971</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>124629</t>
+          <t>135323</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>326935</t>
+          <t>351049</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>308563</t>
+          <t>331815</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>347459</t>
+          <t>372683</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>66,53%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>38322</t>
+          <t>43490</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>27752</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>20227</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>50595</t>
+          <t>59719</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>40282</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>63216</t>
+          <t>73332</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>21783</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>22782</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>31697</t>
+          <t>42321</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>13567</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>19560</t>
+          <t>20981</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15310</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23930</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>13258</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>53,59%</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>816</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4667,12 +4667,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4745,12 +4745,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>437</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>384014</t>
+          <t>439326</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>255714</t>
+          <t>398335</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>451392</t>
+          <t>480334</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>497928</t>
+          <t>554929</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>423386</t>
+          <t>521053</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>541374</t>
+          <t>587603</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>881942</t>
+          <t>994255</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>691675</t>
+          <t>940498</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>977130</t>
+          <t>1043525</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>24970</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>15077</t>
+          <t>24122</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>299486</t>
+          <t>24974</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>55245</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>31386</t>
+          <t>40842</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>377216</t>
+          <t>76760</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1531325</t>
+          <t>1408006</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1453831</t>
+          <t>1363077</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1670403</t>
+          <t>1449760</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>879809</t>
+          <t>920448</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>735063</t>
+          <t>884410</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>936876</t>
+          <t>953875</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2411135</t>
+          <t>2328455</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2257817</t>
+          <t>2271399</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2597394</t>
+          <t>2384275</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>158560</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>80741</t>
+          <t>132684</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>158237</t>
+          <t>189371</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>148643</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>119889</t>
+          <t>149700</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>174491</t>
+          <t>195560</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>276625</t>
+          <t>331335</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>217072</t>
+          <t>294712</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>317880</t>
+          <t>366744</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>16711</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6064,32 +6064,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>48465</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>99132</t>
+          <t>108552</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6099,32 +6099,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>40003</t>
+          <t>49386</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>66794</t>
+          <t>77749</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6134,32 +6134,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>125623</t>
+          <t>148852</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>95297</t>
+          <t>126351</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>152098</t>
+          <t>177170</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
           <t>3,67%</t>
         </is>
       </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64D$andando_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Edad-trans_orig.xlsx
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52600</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34930</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66726</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49614</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36623</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62096</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>102214</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82160</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>123104</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -1054,112 +1054,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16046</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19512</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30601</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53218</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -1167,112 +1167,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52600</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66726</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>49614</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>62096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>102214</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>123104</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -1280,112 +1280,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>30601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>53218</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -1623,112 +1623,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>284006</t>
+          <t>24822</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>261756</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>305995</t>
+          <t>38970</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>192900</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>174582</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>210496</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>476907</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>448344</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>509677</t>
+          <t>54927</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -1736,112 +1736,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32478</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20419</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49304</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33677</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22912</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46613</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>66155</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50594</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86153</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1849,112 +1849,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>176</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>284006</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>261756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>305995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>181</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>192900</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>174582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>210496</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>357</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>476907</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>448344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>509677</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -1962,112 +1962,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>20419</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38970</t>
+          <t>49304</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>22912</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18857</t>
+          <t>46613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>52</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>35809</t>
+          <t>66155</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>50594</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>54927</t>
+          <t>86153</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -2305,112 +2305,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>408355</t>
+          <t>23348</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>385208</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>427829</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>253953</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>238284</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>270360</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>662308</t>
+          <t>37433</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>636813</t>
+          <t>27304</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>688494</t>
+          <t>51597</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -2418,112 +2418,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43602</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30728</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57580</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26243</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45814</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>78133</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63538</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96356</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2531,112 +2531,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>361</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>408355</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>385208</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>427829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>355</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>253953</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238284</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>270360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>716</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>662308</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>636813</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>688494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -2644,112 +2644,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>43602</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37234</t>
+          <t>57580</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>34531</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>45814</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>81</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>37433</t>
+          <t>78133</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27304</t>
+          <t>63538</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>51597</t>
+          <t>96356</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -2987,112 +2987,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>426416</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>404635</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>444088</t>
+          <t>25667</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>292663</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>275989</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>307534</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>719079</t>
+          <t>34753</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>691534</t>
+          <t>25469</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>743507</t>
+          <t>46549</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -3100,112 +3100,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>33650</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23505</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>11264</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>54986</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43338</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66997</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>88636</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73099</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>105932</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -3213,112 +3213,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>413</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>426416</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>404635</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>444088</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>465</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>292663</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>275989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>307534</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>878</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>719079</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>691534</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14784</t>
+          <t>743507</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>74,46%</t>
         </is>
       </c>
     </row>
@@ -3326,112 +3326,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>33650</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>23505</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>54986</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>43338</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>66997</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>107</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>34753</t>
+          <t>88636</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>25469</t>
+          <t>73099</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>46549</t>
+          <t>105932</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -3669,112 +3669,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>227382</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>209890</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>243719</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>123667</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>110971</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>135323</t>
+          <t>21783</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>351049</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>331815</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>372683</t>
+          <t>42321</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -3782,112 +3782,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22677</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43490</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>27752</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>59719</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>47352</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>73332</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3895,112 +3895,112 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>248</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>227382</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>209890</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>243719</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>212</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123667</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110971</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135323</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>460</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>351049</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>331815</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>372683</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>66,53%</t>
         </is>
       </c>
     </row>
@@ -4008,112 +4008,112 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>43490</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>27752</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9707</t>
+          <t>20227</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>75</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>31391</t>
+          <t>59719</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>42321</t>
+          <t>73332</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -4351,112 +4351,112 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>16012</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>437</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>723</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4499,77 +4499,77 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>723</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -4577,112 +4577,112 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>53,59%</t>
         </is>
       </c>
     </row>
@@ -4690,17 +4690,17 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>816</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4725,77 +4725,77 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -5033,112 +5033,112 @@
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>1817</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>48,81%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="W42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>1817</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>48,81%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -5259,112 +5259,112 @@
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>48,81%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>48,81%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -5715,112 +5715,112 @@
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1408006</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1363077</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1449760</t>
+          <t>108552</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>920448</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>884410</t>
+          <t>49386</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>953875</t>
+          <t>77749</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>152</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2328455</t>
+          <t>148852</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2271399</t>
+          <t>126351</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2384275</t>
+          <t>177170</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -5828,112 +5828,112 @@
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>158560</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>132684</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>189371</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>172774</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>149700</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>195560</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>331335</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>294712</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -5941,112 +5941,112 @@
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>21439</t>
+          <t>1408006</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>1363077</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>33169</t>
+          <t>1449760</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>920448</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>884410</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>953875</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>34384</t>
+          <t>2328455</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>2271399</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>2384275</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -6054,112 +6054,112 @@
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>86023</t>
+          <t>158560</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>67045</t>
+          <t>132684</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>108552</t>
+          <t>189371</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>208</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>62829</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>49386</t>
+          <t>149700</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>77749</t>
+          <t>195560</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>340</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>148852</t>
+          <t>331335</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>126351</t>
+          <t>294712</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>177170</t>
+          <t>366744</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
